--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.57027462980652</v>
+        <v>3.01766962734356</v>
       </c>
       <c r="D2" t="n">
-        <v>18.51859863552154</v>
+        <v>3.00927227827225</v>
       </c>
       <c r="E2" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F2" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.374951445971378</v>
+        <v>1.523429609970349</v>
       </c>
       <c r="D3" t="n">
-        <v>9.531385719062454</v>
+        <v>1.548850179347649</v>
       </c>
       <c r="E3" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F3" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.12110688016138</v>
+        <v>6.357179868026224</v>
       </c>
       <c r="D4" t="n">
-        <v>38.93887621854265</v>
+        <v>6.32756738551318</v>
       </c>
       <c r="E4" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F4" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.96412388457679</v>
+        <v>4.706670131243728</v>
       </c>
       <c r="D5" t="n">
-        <v>29.45218166341319</v>
+        <v>4.785979520304643</v>
       </c>
       <c r="E5" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F5" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.9110980435316</v>
+        <v>4.048053432073885</v>
       </c>
       <c r="D6" t="n">
-        <v>24.4320900309656</v>
+        <v>3.97021463003191</v>
       </c>
       <c r="E6" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F6" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.45635270458457</v>
+        <v>8.524157314494994</v>
       </c>
       <c r="D7" t="n">
-        <v>51.77559910971248</v>
+        <v>8.413534855328278</v>
       </c>
       <c r="E7" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F7" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.16118771750175</v>
+        <v>7.338693004094034</v>
       </c>
       <c r="D8" t="n">
-        <v>44.50544965515355</v>
+        <v>7.232135568962453</v>
       </c>
       <c r="E8" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F8" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.20330105635551</v>
+        <v>8.320536421657771</v>
       </c>
       <c r="D9" t="n">
-        <v>50.47482250936633</v>
+        <v>8.20215865777203</v>
       </c>
       <c r="E9" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F9" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.049413282842225</v>
+        <v>1.145529658461861</v>
       </c>
       <c r="D10" t="n">
-        <v>7.753443800176692</v>
+        <v>1.259934617528712</v>
       </c>
       <c r="E10" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F10" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.67181718293669</v>
+        <v>5.471670292227213</v>
       </c>
       <c r="D11" t="n">
-        <v>32.9614038821634</v>
+        <v>5.356228130851553</v>
       </c>
       <c r="E11" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F11" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.20625731029113</v>
+        <v>7.508516812922308</v>
       </c>
       <c r="D12" t="n">
-        <v>45.47735889990898</v>
+        <v>7.390070821235209</v>
       </c>
       <c r="E12" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F12" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>18.77519655647963</v>
+        <v>3.05096944042794</v>
       </c>
       <c r="D13" t="n">
-        <v>19.13504949226116</v>
+        <v>3.109445542492439</v>
       </c>
       <c r="E13" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F13" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.07696524312394</v>
+        <v>2.937506852007641</v>
       </c>
       <c r="D14" t="n">
-        <v>18.04093460727116</v>
+        <v>2.931651873681564</v>
       </c>
       <c r="E14" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F14" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.87991940763405</v>
+        <v>5.505486903740533</v>
       </c>
       <c r="D15" t="n">
-        <v>34.4192369036457</v>
+        <v>5.593125996842427</v>
       </c>
       <c r="E15" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F15" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>39.26684223500391</v>
+        <v>6.380861863188135</v>
       </c>
       <c r="D16" t="n">
-        <v>38.6522579725142</v>
+        <v>6.280991920533558</v>
       </c>
       <c r="E16" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F16" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>26.23057641508814</v>
+        <v>4.262468667451823</v>
       </c>
       <c r="D17" t="n">
-        <v>26.42019258857993</v>
+        <v>4.293281295644238</v>
       </c>
       <c r="E17" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F17" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>53.98199272968513</v>
+        <v>8.772073818573833</v>
       </c>
       <c r="D18" t="n">
-        <v>54.60361725903343</v>
+        <v>8.873087804592933</v>
       </c>
       <c r="E18" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F18" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>30.38763198353763</v>
+        <v>4.937990197324866</v>
       </c>
       <c r="D19" t="n">
-        <v>30.21169795036545</v>
+        <v>4.909400916934385</v>
       </c>
       <c r="E19" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F19" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>35.97798964739105</v>
+        <v>5.846423317701046</v>
       </c>
       <c r="D20" t="n">
-        <v>35.61409090823356</v>
+        <v>5.787289772587954</v>
       </c>
       <c r="E20" t="n">
-        <v>13.66625851521631</v>
+        <v>2.220767008722651</v>
       </c>
       <c r="F20" t="n">
-        <v>13.42831848644187</v>
+        <v>2.182101754046804</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
